--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3099FFBA-2899-40DC-97A8-8ADBF3E759FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4805BDAAA1C93E744EC68F1D43E05A01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE0C7DE6-D042-4348-88FE-42EDAC2C7F31}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 09-09-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 14-09-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4805BDAAA1C93E744EC68F1D43E05A01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE0C7DE6-D042-4348-88FE-42EDAC2C7F31}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4805BDAAA1C93EB20603B7AB43E05A01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCB43078-238B-4301-A076-96547FE76179}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4805BDAAA1C93EB20603B7AB43E05A01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCB43078-238B-4301-A076-96547FE76179}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6238066E-77EC-46ED-BF85-5984B8A66AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6238066E-77EC-46ED-BF85-5984B8A66AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEACB5B9-970B-41AD-AA58-75BBDED48575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 14-09-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 17-09-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEACB5B9-970B-41AD-AA58-75BBDED48575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C55B1D-FF77-4FA5-A257-6189EE77FAB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C55B1D-FF77-4FA5-A257-6189EE77FAB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4805BDAAA1C93E170E45874742E05A01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B014F17-E797-4AD2-8ACE-73DE07E029BC}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 17-09-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 21-09-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4805BDAAA1C93E170E45874742E05A01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B014F17-E797-4AD2-8ACE-73DE07E029BC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB3A779-2FE9-44C4-AE0A-BD4BD179D6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB3A779-2FE9-44C4-AE0A-BD4BD179D6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC37B66-13A2-4C55-91D6-861D0BE74D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 21-09-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 22-09-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC37B66-13A2-4C55-91D6-861D0BE74D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D70E031-8464-433D-B720-CBD4AABD5CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D70E031-8464-433D-B720-CBD4AABD5CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B169B2-A7EC-4FEB-B582-2DFEEB197C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 22-09-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 23-09-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B169B2-A7EC-4FEB-B582-2DFEEB197C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4805BDAAA1C93EA17681900B42E05A01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B2A5B34-CC15-4526-981A-D7B27C802297}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 23-09-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 24-09-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4805BDAAA1C93EA17681900B42E05A01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B2A5B34-CC15-4526-981A-D7B27C802297}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEFAAF7-E7D4-46F3-9763-1A0F18152DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 24-09-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 28-09-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEFAAF7-E7D4-46F3-9763-1A0F18152DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4805BDAAA1C93ED8CE00B42543E05A01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F028203-AD34-4750-A2C5-738641C73164}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 28-09-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 02-10-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D70E031-8464-433D-B720-CBD4AABD5CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04169E4D-CE33-49FA-93B1-607B1E31B0FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 22-09-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 07-10-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4805BDAAA1C93ED8CE00B42543E05A01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F028203-AD34-4750-A2C5-738641C73164}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A1C9F7-AF7F-4269-B1C8-0DA5F89C1703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 02-10-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 07-10-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A1C9F7-AF7F-4269-B1C8-0DA5F89C1703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4805BDAAA1C93EB4DE42B7F542E05A05" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2470FF3F-E1C8-42E9-9A01-47682839CBE0}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 07-10-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 08-10-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4805BDAAA1C93EB4DE42B7F542E05A05" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2470FF3F-E1C8-42E9-9A01-47682839CBE0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F03465B-F9D5-430E-9427-5EEA0E2616EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 08-10-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 09-10-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F03465B-F9D5-430E-9427-5EEA0E2616EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1E37F1-C6DC-4A79-B266-33D7DC24327A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1E37F1-C6DC-4A79-B266-33D7DC24327A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB4805BDAAA1C93EE08E459BC342E05A05" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53923B9F-1235-4589-A8C9-628CA399DB7D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 09-10-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 23-10-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
